--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/4966-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/4966-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C442FC3-C02D-4B2F-BD78-9A1DD63315B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{221D7367-5DC7-4D24-8549-F21A94375E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{89E4C0F0-A9A2-419E-A82B-FA2B7AC5E82C}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{0BC22BD1-4C44-483D-9BF8-649225D8EA30}"/>
   </bookViews>
   <sheets>
     <sheet name="4966-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1540,25 +1540,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87496CB1-DF1D-4F1B-A087-8F3CBCDC6FD8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B9424C6-6A39-49E7-9A13-E18A2E24B286}">
   <dimension ref="A1:R35"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1586,7 +1586,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1616,7 +1616,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1712,7 +1712,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1792,7 +1792,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="51">
         <v>2024</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>1.46</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>27</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>27</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="49">
         <v>2023</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>27</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>27</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>2.23</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="51">
         <v>2022</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>27</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>27</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="49">
         <v>2021</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>1.54</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2622,7 +2622,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2020</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="49">
         <v>2019</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="51">
         <v>2018</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2017</v>
       </c>
@@ -3006,7 +3006,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="51">
         <v>2016</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="49">
         <v>2015</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="51">
         <v>2014</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="49">
         <v>2013</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>2.61</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2012</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="49">
         <v>2011</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="51" t="s">
         <v>51</v>
       </c>
